--- a/output/pdf_financials_xlsx/NXR.UN.xlsx
+++ b/output/pdf_financials_xlsx/NXR.UN.xlsx
@@ -1063,19 +1063,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.012755</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.023091</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001176</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.008697999999999999</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -2013,19 +2013,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.322935</v>
+        <v>-0.33569</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.322935</v>
+        <v>-0.346026</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>9.174234999999999</v>
+        <v>9.173059</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>5.740787</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>10.493614</v>
+        <v>10.484916</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>15.714792</v>
@@ -2121,19 +2121,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.322935</v>
+        <v>-0.33569</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.322935</v>
+        <v>-0.346026</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>9.174234999999999</v>
+        <v>9.173059</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>5.740787</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>10.493614</v>
+        <v>10.484916</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>15.714792</v>
@@ -2412,13 +2412,13 @@
         <v>1.152168</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.904023</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>4.253771</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>3.354169</v>
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
@@ -2426,22 +2426,22 @@
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>13.993</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>82.279</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>11.533</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>5.918</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>11.532</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>6.111</v>
       </c>
       <c r="P34" s="1" t="inlineStr">
         <is>
@@ -2524,13 +2524,13 @@
         <v>1.152168</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.904023</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>4.253771</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>3.354169</v>
       </c>
       <c r="I36" s="1" t="inlineStr">
         <is>
@@ -2538,22 +2538,22 @@
         </is>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>13.993</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>82.279</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>11.533</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>5.918</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>11.532</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>6.111</v>
       </c>
       <c r="P36" s="1" t="inlineStr">
         <is>
@@ -3210,22 +3210,22 @@
         </is>
       </c>
       <c r="J48" s="3" t="n">
-        <v>29.192</v>
+        <v>15.199</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>94.76900000000001</v>
+        <v>12.49</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>101.737</v>
+        <v>90.20399999999999</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>54.6</v>
+        <v>48.682</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>110.592</v>
+        <v>99.06</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>91.714</v>
+        <v>85.60299999999999</v>
       </c>
       <c r="P48" s="1" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -15488,7 +15488,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -42019,7 +42019,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -46908,7 +46908,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -50868,7 +50868,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -56502,7 +56502,7 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
@@ -58395,7 +58395,7 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
@@ -62260,7 +62260,7 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
@@ -64699,7 +64699,7 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
@@ -64792,7 +64792,7 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
@@ -67417,7 +67417,7 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
@@ -70046,7 +70046,7 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E693" s="5" t="n">
